--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N52_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N52_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.96068742525539</v>
+        <v>6.331111706604002</v>
       </c>
       <c r="D2" t="n">
-        <v>39.65766967252286</v>
+        <v>6.444371321784964</v>
       </c>
       <c r="E2" t="n">
-        <v>25.86604701696888</v>
+        <v>4.203232640257443</v>
       </c>
       <c r="F2" t="n">
-        <v>13.17440740764026</v>
+        <v>2.140841203741542</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.26726870177182</v>
+        <v>5.893431164037921</v>
       </c>
       <c r="D3" t="n">
-        <v>36.81071508743962</v>
+        <v>5.981741201708938</v>
       </c>
       <c r="E3" t="n">
-        <v>25.86604701696888</v>
+        <v>4.203232640257443</v>
       </c>
       <c r="F3" t="n">
-        <v>13.17440740764026</v>
+        <v>2.140841203741542</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5.909354178647118</v>
+        <v>0.9602700540301568</v>
       </c>
       <c r="D4" t="n">
-        <v>6.27447724635612</v>
+        <v>1.01960255253287</v>
       </c>
       <c r="E4" t="n">
-        <v>25.86604701696888</v>
+        <v>4.203232640257443</v>
       </c>
       <c r="F4" t="n">
-        <v>13.17440740764026</v>
+        <v>2.140841203741542</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.86978492722683</v>
+        <v>3.22884005067436</v>
       </c>
       <c r="D5" t="n">
-        <v>19.85483902119997</v>
+        <v>3.226411340944995</v>
       </c>
       <c r="E5" t="n">
-        <v>25.86604701696888</v>
+        <v>4.203232640257443</v>
       </c>
       <c r="F5" t="n">
-        <v>13.17440740764026</v>
+        <v>2.140841203741542</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.75780079759591</v>
+        <v>4.023142629609336</v>
       </c>
       <c r="D6" t="n">
-        <v>24.15588149482281</v>
+        <v>3.925330742908708</v>
       </c>
       <c r="E6" t="n">
-        <v>25.86604701696888</v>
+        <v>4.203232640257443</v>
       </c>
       <c r="F6" t="n">
-        <v>13.17440740764026</v>
+        <v>2.140841203741542</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.63444938037555</v>
+        <v>6.115598024311027</v>
       </c>
       <c r="D7" t="n">
-        <v>37.06189506685165</v>
+        <v>6.022557948363393</v>
       </c>
       <c r="E7" t="n">
-        <v>25.86604701696888</v>
+        <v>4.203232640257443</v>
       </c>
       <c r="F7" t="n">
-        <v>13.17440740764026</v>
+        <v>2.140841203741542</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.5849398830935</v>
+        <v>6.757552731002694</v>
       </c>
       <c r="D8" t="n">
-        <v>40.88660013817027</v>
+        <v>6.64407252245267</v>
       </c>
       <c r="E8" t="n">
-        <v>25.86604701696888</v>
+        <v>4.203232640257443</v>
       </c>
       <c r="F8" t="n">
-        <v>13.17440740764026</v>
+        <v>2.140841203741542</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>99.65784508776048</v>
+        <v>16.19439982676108</v>
       </c>
       <c r="D9" t="n">
-        <v>8.280424981261707</v>
+        <v>1.345569059455027</v>
       </c>
       <c r="E9" t="n">
-        <v>25.86604701696888</v>
+        <v>4.203232640257443</v>
       </c>
       <c r="F9" t="n">
-        <v>13.17440740764026</v>
+        <v>2.140841203741542</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
